--- a/images/fig-summary/fig-summary.xlsx
+++ b/images/fig-summary/fig-summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slope\Documents\meteors\images\fig-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0372F97-1AFF-493C-8FBC-C5D007CE056E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EDF0ED8-6518-458A-A6A3-2F9E8D9B10BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="32220" windowHeight="20220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="32220" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="速の章" sheetId="6" r:id="rId1"/>
@@ -5622,26 +5622,6 @@
               <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
               <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
             </a:rPr>
-            <a:t>またはその変化</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600" kern="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600" kern="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-              <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            </a:rPr>
             <a:t>が付く神</a:t>
           </a:r>
         </a:p>
@@ -5781,26 +5761,6 @@
               <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
             </a:rPr>
             <a:t>「ミカ」</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600" kern="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600" kern="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-              <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            </a:rPr>
-            <a:t>またはその変化</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600" kern="1200">
             <a:solidFill>
@@ -6292,26 +6252,6 @@
               <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
               <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
             </a:rPr>
-            <a:t>またはその変化</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600" kern="1200">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600" kern="1200">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-              <a:ea typeface="游明朝" panose="02020400000000000000" pitchFamily="18" charset="-128"/>
-            </a:rPr>
             <a:t>が付く神</a:t>
           </a:r>
         </a:p>
